--- a/Alldesk.xlsx
+++ b/Alldesk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\py\Alldesk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3598049-BBC7-41C8-AC46-C52E4935169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611BBF83-9504-4F31-95D3-09E9D2146A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21877" yWindow="1357" windowWidth="17339" windowHeight="11858" xr2:uid="{1CFA8F19-ADE6-4D82-9080-2F984CC26190}"/>
   </bookViews>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="32">
-  <si>
-    <t>電腦名稱</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>密碼</t>
   </si>
@@ -95,35 +92,52 @@
     <t>Pntech54294093!</t>
   </si>
   <si>
-    <t>AnyDeskID</t>
-  </si>
-  <si>
     <t>博能SOYAL</t>
   </si>
   <si>
     <t>server-PC</t>
   </si>
   <si>
-    <t>Item</t>
+    <t>192.168.2.6</t>
   </si>
   <si>
     <t>URL</t>
-  </si>
-  <si>
-    <t>port</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>192.168.2.6</t>
-  </si>
-  <si>
-    <t>永雋SOYAL</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>RustdeskID</t>
+    <t>lioil</t>
+  </si>
+  <si>
+    <t>lioil.ddnsfree.com</t>
+  </si>
+  <si>
+    <t>Blue0324</t>
+  </si>
+  <si>
+    <t>PTW</t>
+  </si>
+  <si>
+    <t>ptw.ddnsfree.com</t>
+  </si>
+  <si>
+    <t>LiBoDe</t>
+  </si>
+  <si>
+    <t>libode.ddnsfree.com</t>
+  </si>
+  <si>
+    <t>EverduraSOYAL</t>
+  </si>
+  <si>
+    <t>埠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>設備名稱</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1143,200 +1157,200 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>162136755</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>223150760</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>328779081</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>1857739076</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>242765848</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2">
         <v>2068572</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
         <v>44068066</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>1779175340</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
         <v>440820085</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2">
         <v>373061491</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2">
         <v>304919441</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
         <v>242765979</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2">
         <v>17606194</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2">
         <v>17606219</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2">
         <v>17599464</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2">
         <v>17599473</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="2">
         <v>1725360045</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1358,178 +1372,178 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2">
         <v>516762580</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>540521973</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2">
         <v>1228120787</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>1304589278</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2">
         <v>1953043777</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2">
         <v>423427369</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>1196837742</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>1828597468</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
         <v>508737724</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="2">
         <v>1275546571</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
         <v>608630403</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>1608806423</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>1978506079</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2">
         <v>1769992080</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2">
         <v>244486783</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1540,41 +1554,83 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6498F7AC-84E3-4FB2-9EF7-D112C3DA6181}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.9296875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2">
         <v>90328511</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D5" s="2">
         <v>5900</v>
       </c>
     </row>

--- a/Alldesk.xlsx
+++ b/Alldesk.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\py\Alldesk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611BBF83-9504-4F31-95D3-09E9D2146A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7207430-F0E3-4652-80A8-6EBC4FB62146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21877" yWindow="1357" windowWidth="17339" windowHeight="11858" xr2:uid="{1CFA8F19-ADE6-4D82-9080-2F984CC26190}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{1CFA8F19-ADE6-4D82-9080-2F984CC26190}"/>
   </bookViews>
   <sheets>
-    <sheet name="rustdesk" sheetId="1" r:id="rId1"/>
-    <sheet name="anydesk" sheetId="2" r:id="rId2"/>
-    <sheet name="VNC" sheetId="3" r:id="rId3"/>
+    <sheet name="RustDesk" sheetId="1" r:id="rId1"/>
+    <sheet name="AnyDesk" sheetId="2" r:id="rId2"/>
+    <sheet name="TightVNC" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="100">
   <si>
     <t>密碼</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Server-PC</t>
   </si>
   <si>
-    <t>ICONICS9-PC</t>
-  </si>
-  <si>
     <t>gogoro-PC</t>
   </si>
   <si>
@@ -68,22 +65,7 @@
     <t>寶高 SCADA</t>
   </si>
   <si>
-    <t>永雋科技 SOYAL</t>
-  </si>
-  <si>
     <t>Panel-PC</t>
-  </si>
-  <si>
-    <t>謙王</t>
-  </si>
-  <si>
-    <t>和境善捷段</t>
-  </si>
-  <si>
-    <t>竹科匯</t>
-  </si>
-  <si>
-    <t>鶯歌家自慢</t>
   </si>
   <si>
     <t>博能科技 SOYAL</t>
@@ -139,6 +121,216 @@
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>emily-NB</t>
+  </si>
+  <si>
+    <t>blue5200</t>
+  </si>
+  <si>
+    <t>FEABC-PC</t>
+  </si>
+  <si>
+    <t>FEABC-PC2</t>
+  </si>
+  <si>
+    <t>walter-PC</t>
+  </si>
+  <si>
+    <t>wayne-NB</t>
+  </si>
+  <si>
+    <t>lioil-VM</t>
+  </si>
+  <si>
+    <t>lioil-VMM</t>
+  </si>
+  <si>
+    <t>lioil-PC</t>
+  </si>
+  <si>
+    <t>Blue0324!</t>
+  </si>
+  <si>
+    <t>lucy-PC</t>
+  </si>
+  <si>
+    <t>migo-NB</t>
+  </si>
+  <si>
+    <t>turbo-PC</t>
+  </si>
+  <si>
+    <t>蔡增仲-VMM</t>
+  </si>
+  <si>
+    <t>陳靜白-PC</t>
+  </si>
+  <si>
+    <t>user00(蔡增仲)</t>
+  </si>
+  <si>
+    <t>user01(蕭咸文)</t>
+  </si>
+  <si>
+    <t>m8KN6)kN</t>
+  </si>
+  <si>
+    <t>user02()</t>
+  </si>
+  <si>
+    <t>U01e*$C/</t>
+  </si>
+  <si>
+    <t>user03(莊宥岑)</t>
+  </si>
+  <si>
+    <t>user04(蘇東泰)</t>
+  </si>
+  <si>
+    <t>Ys_G#y6u</t>
+  </si>
+  <si>
+    <t>user05(鍾承勳)</t>
+  </si>
+  <si>
+    <t>r_6Gx1t\</t>
+  </si>
+  <si>
+    <t>user06(賀欣儀)</t>
+  </si>
+  <si>
+    <t>FI=nwfo5</t>
+  </si>
+  <si>
+    <t>user07(杜睿宸)</t>
+  </si>
+  <si>
+    <t>user08(羅伊岑)</t>
+  </si>
+  <si>
+    <t>A#w#82Nb</t>
+  </si>
+  <si>
+    <t>user09(NB)</t>
+  </si>
+  <si>
+    <t>yachun-PC</t>
+  </si>
+  <si>
+    <t>永雋 SOYAL</t>
+  </si>
+  <si>
+    <t>吳鎮耀-NB</t>
+  </si>
+  <si>
+    <t>李秀琴-NB2</t>
+  </si>
+  <si>
+    <t>李秀琴-NB</t>
+  </si>
+  <si>
+    <t>李秀琴-phone</t>
+  </si>
+  <si>
+    <t>李秀暖win10</t>
+  </si>
+  <si>
+    <t>李秀暖win11</t>
+  </si>
+  <si>
+    <t>周信良-PC</t>
+  </si>
+  <si>
+    <t>邱威迪-NB</t>
+  </si>
+  <si>
+    <t>邱威迪-PC</t>
+  </si>
+  <si>
+    <t>邱威迪2-PC</t>
+  </si>
+  <si>
+    <t>陳耀輝-PC</t>
+  </si>
+  <si>
+    <t>陳耀輝-PC2</t>
+  </si>
+  <si>
+    <t>彭心儀-PC</t>
+  </si>
+  <si>
+    <t>彭雙成1-PC</t>
+  </si>
+  <si>
+    <t>彭雙成2-PC</t>
+  </si>
+  <si>
+    <t>彭雙成3-PC</t>
+  </si>
+  <si>
+    <t>游秀淳1F-PC</t>
+  </si>
+  <si>
+    <t>游秀淳2F-PC</t>
+  </si>
+  <si>
+    <t>黃睿頎-PC</t>
+  </si>
+  <si>
+    <t>科博館</t>
+  </si>
+  <si>
+    <t>台北地院 SCADA</t>
+  </si>
+  <si>
+    <t>地檢署 SYSTEM</t>
+  </si>
+  <si>
+    <t>地檢署 SCADA</t>
+  </si>
+  <si>
+    <t>法務部 SCADA</t>
+  </si>
+  <si>
+    <t>致新科技 SCADA</t>
+  </si>
+  <si>
+    <t>c0933976189</t>
+  </si>
+  <si>
+    <t>新保大樓 SCADA</t>
+  </si>
+  <si>
+    <t>新保大樓5F</t>
+  </si>
+  <si>
+    <t>北投享溫泉 SCADA</t>
+  </si>
+  <si>
+    <t>water28928288house</t>
+  </si>
+  <si>
+    <t>北投享溫泉2 SCADA</t>
+  </si>
+  <si>
+    <t>北投享溫泉3 SCADA</t>
+  </si>
+  <si>
+    <t>暐順 SCADA</t>
+  </si>
+  <si>
+    <t>李秀暖-win11</t>
+  </si>
+  <si>
+    <t>新保大樓 5F</t>
+  </si>
+  <si>
+    <t>Wh28928288</t>
+  </si>
+  <si>
+    <t>北投享溫泉(櫃台)-PC</t>
   </si>
 </sst>
 </file>
@@ -1146,10 +1338,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3FBB5F-9081-4A93-A9A9-04AE290E38A1}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.265625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.9296875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.06640625" style="2"/>
@@ -1157,10 +1349,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1201,32 +1393,32 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2">
-        <v>1857739076</v>
+        <v>533392223</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2">
-        <v>242765848</v>
+        <v>429101551</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>2068572</v>
+        <v>242765848</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>2</v>
@@ -1234,54 +1426,54 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2">
-        <v>44068066</v>
+        <v>1918380113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2">
-        <v>1779175340</v>
+        <v>426677725</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2">
-        <v>440820085</v>
+        <v>117767810</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2">
-        <v>373061491</v>
+        <v>1352706</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>304919441</v>
+        <v>242765979</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>2</v>
@@ -1289,68 +1481,431 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2">
-        <v>242765979</v>
+        <v>340337553</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2">
-        <v>17606194</v>
+        <v>505507640</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2">
-        <v>17606219</v>
+        <v>505507601</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
-        <v>17599464</v>
+        <v>314418619</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
-        <v>17599473</v>
+        <v>314470396</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
+        <v>20212705</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="2">
+        <v>228516601</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="2">
+        <v>420215615</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2">
+        <v>44043034</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2">
+        <v>405721595</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="2">
+        <v>118425841</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1857739076</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1416753381</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2">
         <v>1725360045</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>20</v>
+      <c r="C26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2">
+        <v>101855588</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2">
+        <v>484004133</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="2">
+        <v>363841468</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="2">
+        <v>1767692325</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2">
+        <v>379684599</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2">
+        <v>24886589</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="2">
+        <v>11996964</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="2">
+        <v>23240752</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="2">
+        <v>82987959</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1818654889</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="2">
+        <v>382285953</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="2">
+        <v>76020948</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="2">
+        <v>47398667</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="2">
+        <v>535728887</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="2">
+        <v>509656325</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="2">
+        <v>117558862</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="2">
+        <v>1172277522</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1651963476</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="2">
+        <v>515768677</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="2">
+        <v>440820085</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="2">
+        <v>373061491</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2">
+        <v>44068066</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2068572</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1395994989</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="2">
+        <v>402863565</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1361,21 +1916,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17D148A-02BB-4917-A221-ECA0604AE000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultColWidth="13.59765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.53125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.86328125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.9296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.06640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="13.59765625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1383,32 +1938,32 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>516762580</v>
+        <v>540521973</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2">
-        <v>540521973</v>
+        <v>1163878181</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>1228120787</v>
+        <v>1275546571</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>2</v>
@@ -1416,32 +1971,32 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2">
-        <v>1304589278</v>
+        <v>1058831515</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2">
-        <v>1953043777</v>
+        <v>1435248711</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>423427369</v>
+        <v>1828597468</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>2</v>
@@ -1449,101 +2004,695 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2">
-        <v>1196837742</v>
+        <v>1665308730</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2">
-        <v>1828597468</v>
+        <v>636599678</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2">
-        <v>508737724</v>
+        <v>467517298</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2">
-        <v>1275546571</v>
+        <v>787983489</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2">
-        <v>608630403</v>
+        <v>1622676015</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2">
-        <v>1608806423</v>
+        <v>1464756719</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B14" s="2">
-        <v>1978506079</v>
+        <v>170036718</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2">
-        <v>1769992080</v>
+        <v>1333165155</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2">
-        <v>244486783</v>
+        <v>928386444</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2">
+        <v>988775006</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="2">
+        <v>994167457</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1353674292</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1095981159</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1242096384</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1316892957</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1017388669</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1837470523</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1541843604</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1124894043</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1528929699</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1286819335</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1361736160</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2">
+        <v>1177230138</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="2">
+        <v>1228120787</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="2">
+        <v>571812724</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="2">
+        <v>516762580</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="2">
+        <v>1494049005</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1729505566</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1689636809</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1053939944</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="2">
+        <v>556558910</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1595466432</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="2">
+        <v>1138660391</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="2">
+        <v>1577856617</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="2">
+        <v>1947941157</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="2">
+        <v>1337950825</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1464058675</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="2">
+        <v>1707444300</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="2">
+        <v>623592888</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="2">
+        <v>1817088987</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="2">
+        <v>677482988</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="2">
+        <v>527173757</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="2">
+        <v>1161780580</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="2">
+        <v>1626221025</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="2">
+        <v>704592803</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="2">
+        <v>378232603</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="2">
+        <v>248082645</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="2">
+        <v>1344781079</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="2">
+        <v>1579258104</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" s="2">
+        <v>458569245</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="2">
+        <v>719552704</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1507809143</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B60" s="2">
+        <v>1839273670</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" s="2">
+        <v>591968037</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" s="2">
+        <v>1140316182</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1906233132</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B64" s="2">
+        <v>720090893</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" s="2">
+        <v>423427369</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="2">
+        <v>608630403</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="2">
+        <v>1953043777</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="2">
+        <v>1196837742</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="2">
+        <v>1152555295</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="2">
+        <v>1925223104</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1566,27 +2715,27 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2">
         <v>5900</v>
@@ -1594,13 +2743,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2">
         <v>5900</v>
@@ -1608,13 +2757,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2">
         <v>5900</v>
@@ -1622,10 +2771,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2">
         <v>90328511</v>

--- a/Alldesk.xlsx
+++ b/Alldesk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\py\Alldesk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF28711C-6777-48EF-BA4E-779F9197E1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798E39B4-AE24-49B4-BA4D-48570EE5E96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="16395" activeTab="2" xr2:uid="{1CFA8F19-ADE6-4D82-9080-2F984CC26190}"/>
+    <workbookView xWindow="1882" yWindow="1972" windowWidth="17340" windowHeight="11858" xr2:uid="{1CFA8F19-ADE6-4D82-9080-2F984CC26190}"/>
   </bookViews>
   <sheets>
     <sheet name="RustDesk" sheetId="1" r:id="rId1"/>
@@ -27,58 +27,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>密碼</t>
   </si>
   <si>
-    <t>104-PC</t>
-  </si>
-  <si>
-    <t>Shen+8888</t>
-  </si>
-  <si>
-    <t>CM2.0</t>
-  </si>
-  <si>
-    <t>EV-PC</t>
-  </si>
-  <si>
-    <t>Server-PC</t>
-  </si>
-  <si>
-    <t>gogoro-PC</t>
-  </si>
-  <si>
-    <t>PTW SCADA</t>
-  </si>
-  <si>
-    <t>永彰 SCADA</t>
-  </si>
-  <si>
-    <t>尚順 SCADA</t>
-  </si>
-  <si>
-    <t>麗寶 SCADA</t>
-  </si>
-  <si>
-    <t>寶高 SCADA</t>
-  </si>
-  <si>
-    <t>Panel-PC</t>
-  </si>
-  <si>
-    <t>server-PC</t>
-  </si>
-  <si>
-    <t>192.168.2.6</t>
-  </si>
-  <si>
     <t>URL</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EverduraSOYAL</t>
   </si>
   <si>
     <t>埠</t>
@@ -91,9 +46,6 @@
   <si>
     <t>ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>永雋 SOYAL</t>
   </si>
 </sst>
 </file>
@@ -1101,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3FBB5F-9081-4A93-A9A9-04AE290E38A1}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.265625" style="2" bestFit="1" customWidth="1"/>
@@ -1112,145 +1064,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>162136755</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>223150760</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2">
-        <v>328779081</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>242765848</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2">
-        <v>242765979</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1857739076</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1416753381</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2">
-        <v>440820085</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2">
-        <v>373061491</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="2">
-        <v>44068066</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2068572</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1395994989</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1261,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B17D148A-02BB-4917-A221-ECA0604AE000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultColWidth="13.59765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24.86328125" style="2" bestFit="1" customWidth="1"/>
@@ -1272,112 +1092,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>540521973</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1275546571</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1828597468</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1228120787</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2">
-        <v>423427369</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2">
-        <v>608630403</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1953043777</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1196837742</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1152555295</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1388,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6498F7AC-84E3-4FB2-9EF7-D112C3DA6181}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20" style="2" bestFit="1" customWidth="1"/>
@@ -1400,30 +1121,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="2">
-        <v>90328511</v>
-      </c>
-      <c r="D2" s="2">
-        <v>5900</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
